--- a/store/knowledge-audit-workbook.xlsx
+++ b/store/knowledge-audit-workbook.xlsx
@@ -3,18 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D8A284-8657-4236-8E6A-F3DF6E403E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FB5346C-E0EE-4A7D-B937-493EBBC3A0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30450" yWindow="570" windowWidth="21600" windowHeight="11835" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Implementation Schedule" sheetId="1" r:id="rId1"/>
-    <sheet name="Content Inventory" sheetId="2" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" r:id="rId3"/>
-    <sheet name="Instructions" sheetId="4" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="4" r:id="rId1"/>
+    <sheet name="Implementation Schedule" sheetId="1" r:id="rId2"/>
+    <sheet name="Content Inventory" sheetId="2" r:id="rId3"/>
+    <sheet name="Summary" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Content Inventory'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Content Inventory'!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -1185,6 +1185,213 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFED7D31"/>
+  </sheetPr>
+  <dimension ref="A1:A43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2F5496"/>
@@ -2233,7 +2440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF4472C4"/>
@@ -2487,7 +2694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -2679,211 +2886,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFED7D31"/>
-  </sheetPr>
-  <dimension ref="A1:A43"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="90" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
-        <v>226</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>